--- a/Documents/Initial Db/Employee-BatchUploadTemplate - Batch 1.xlsx
+++ b/Documents/Initial Db/Employee-BatchUploadTemplate - Batch 1.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://filinvest-my.sharepoint.com/personal/sam_amor_onetechfilinvest_com/Documents/Documents/ODMS/Documents/Initial Db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{B7B66A7D-622A-4851-A3B9-3A52FBECBE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23A8BB40-B8A2-4150-B781-F880D4AABA6D}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{B7B66A7D-622A-4851-A3B9-3A52FBECBE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D44AF4B1-749A-495C-853E-79164B5C3027}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Employee" sheetId="1" r:id="rId1"/>
+    <sheet name="Roles" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Employee!$A$1:$I$165</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="631">
   <si>
     <t>Department</t>
   </si>
@@ -1862,13 +1863,67 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>employee001@placeholder.test</t>
+  </si>
+  <si>
+    <t>EMPLOYEE-001</t>
+  </si>
+  <si>
+    <t>Ats Isidro</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>employee002@placeholder.test</t>
+  </si>
+  <si>
+    <t>EMPLOYEE-002</t>
+  </si>
+  <si>
+    <t>Pet Vitan</t>
+  </si>
+  <si>
+    <t>employee003@placeholder.test</t>
+  </si>
+  <si>
+    <t>EMPLOYEE-003</t>
+  </si>
+  <si>
+    <t>Marie Frances Munez</t>
+  </si>
+  <si>
+    <t>Technical Business Partner</t>
+  </si>
+  <si>
+    <t>employee004@placeholder.test</t>
+  </si>
+  <si>
+    <t>EMPLOYEE-004</t>
+  </si>
+  <si>
+    <t>Joey Loayon</t>
+  </si>
+  <si>
+    <t>Bill Code</t>
+  </si>
+  <si>
+    <t>Employee Code</t>
+  </si>
+  <si>
+    <t>Role</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1879,8 +1934,20 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1892,8 +1959,18 @@
         <fgColor rgb="FF00008B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F2A3D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1916,17 +1993,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2259,19 +2355,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="57.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" customWidth="1"/>
+    <col min="2" max="2" width="41.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.81640625" customWidth="1"/>
     <col min="4" max="4" width="27.90625" customWidth="1"/>
-    <col min="5" max="5" width="32.90625" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="6" max="7" width="13.453125" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2293,8 +2389,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" s="4" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2310,11 +2409,8 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -2330,11 +2426,8 @@
       <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2350,11 +2443,8 @@
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2370,11 +2460,8 @@
       <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2390,11 +2477,8 @@
       <c r="E6" t="s">
         <v>32</v>
       </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -2410,11 +2494,8 @@
       <c r="E7" t="s">
         <v>37</v>
       </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -2430,11 +2511,8 @@
       <c r="E8" t="s">
         <v>42</v>
       </c>
-      <c r="G8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -2450,11 +2528,8 @@
       <c r="E9" t="s">
         <v>47</v>
       </c>
-      <c r="G9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -2470,11 +2545,8 @@
       <c r="E10" t="s">
         <v>53</v>
       </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -2490,11 +2562,8 @@
       <c r="E11" t="s">
         <v>53</v>
       </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -2510,11 +2579,8 @@
       <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="G12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2530,11 +2596,8 @@
       <c r="E13" t="s">
         <v>65</v>
       </c>
-      <c r="G13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -2550,11 +2613,8 @@
       <c r="E14" t="s">
         <v>70</v>
       </c>
-      <c r="G14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -2570,11 +2630,8 @@
       <c r="E15" t="s">
         <v>74</v>
       </c>
-      <c r="G15">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -2590,11 +2647,8 @@
       <c r="E16" t="s">
         <v>70</v>
       </c>
-      <c r="G16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2610,11 +2664,8 @@
       <c r="E17" t="s">
         <v>70</v>
       </c>
-      <c r="G17">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>82</v>
       </c>
@@ -2630,11 +2681,8 @@
       <c r="E18" t="s">
         <v>86</v>
       </c>
-      <c r="G18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -2650,11 +2698,8 @@
       <c r="E19" t="s">
         <v>90</v>
       </c>
-      <c r="G19">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -2670,11 +2715,8 @@
       <c r="E20" t="s">
         <v>32</v>
       </c>
-      <c r="G20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>94</v>
       </c>
@@ -2690,11 +2732,8 @@
       <c r="E21" t="s">
         <v>98</v>
       </c>
-      <c r="G21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -2710,11 +2749,8 @@
       <c r="E22" t="s">
         <v>17</v>
       </c>
-      <c r="G22">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>102</v>
       </c>
@@ -2730,11 +2766,8 @@
       <c r="E23" t="s">
         <v>106</v>
       </c>
-      <c r="G23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -2750,11 +2783,8 @@
       <c r="E24" t="s">
         <v>70</v>
       </c>
-      <c r="G24">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -2770,11 +2800,8 @@
       <c r="E25" t="s">
         <v>113</v>
       </c>
-      <c r="G25">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -2790,11 +2817,8 @@
       <c r="E26" t="s">
         <v>117</v>
       </c>
-      <c r="G26">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>94</v>
       </c>
@@ -2810,11 +2834,8 @@
       <c r="E27" t="s">
         <v>121</v>
       </c>
-      <c r="G27">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>122</v>
       </c>
@@ -2830,11 +2851,8 @@
       <c r="E28" t="s">
         <v>126</v>
       </c>
-      <c r="G28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -2850,11 +2868,8 @@
       <c r="E29" t="s">
         <v>130</v>
       </c>
-      <c r="G29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -2870,11 +2885,8 @@
       <c r="E30" t="s">
         <v>134</v>
       </c>
-      <c r="G30">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -2890,11 +2902,8 @@
       <c r="E31" t="s">
         <v>65</v>
       </c>
-      <c r="G31">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -2910,11 +2919,8 @@
       <c r="E32" t="s">
         <v>113</v>
       </c>
-      <c r="G32">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -2930,11 +2936,8 @@
       <c r="E33" t="s">
         <v>27</v>
       </c>
-      <c r="G33">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>144</v>
       </c>
@@ -2950,11 +2953,8 @@
       <c r="E34" t="s">
         <v>27</v>
       </c>
-      <c r="G34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>148</v>
       </c>
@@ -2970,11 +2970,8 @@
       <c r="E35" t="s">
         <v>27</v>
       </c>
-      <c r="G35">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -2990,11 +2987,8 @@
       <c r="E36" t="s">
         <v>156</v>
       </c>
-      <c r="G36">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>61</v>
       </c>
@@ -3010,11 +3004,8 @@
       <c r="E37" t="s">
         <v>65</v>
       </c>
-      <c r="G37">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>57</v>
       </c>
@@ -3030,11 +3021,8 @@
       <c r="E38" t="s">
         <v>27</v>
       </c>
-      <c r="G38">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -3050,11 +3038,8 @@
       <c r="E39" t="s">
         <v>134</v>
       </c>
-      <c r="G39">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -3070,11 +3055,8 @@
       <c r="E40" t="s">
         <v>169</v>
       </c>
-      <c r="G40">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>170</v>
       </c>
@@ -3090,11 +3072,8 @@
       <c r="E41" t="s">
         <v>174</v>
       </c>
-      <c r="G41">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -3110,11 +3089,8 @@
       <c r="E42" t="s">
         <v>178</v>
       </c>
-      <c r="G42">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>148</v>
       </c>
@@ -3130,11 +3106,8 @@
       <c r="E43" t="s">
         <v>182</v>
       </c>
-      <c r="G43">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>183</v>
       </c>
@@ -3150,11 +3123,8 @@
       <c r="E44" t="s">
         <v>70</v>
       </c>
-      <c r="G44">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -3170,11 +3140,8 @@
       <c r="E45" t="s">
         <v>190</v>
       </c>
-      <c r="G45">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>191</v>
       </c>
@@ -3190,11 +3157,8 @@
       <c r="E46" t="s">
         <v>195</v>
       </c>
-      <c r="G46">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -3210,11 +3174,8 @@
       <c r="E47" t="s">
         <v>117</v>
       </c>
-      <c r="G47">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>66</v>
       </c>
@@ -3230,11 +3191,8 @@
       <c r="E48" t="s">
         <v>17</v>
       </c>
-      <c r="G48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -3250,11 +3208,8 @@
       <c r="E49" t="s">
         <v>17</v>
       </c>
-      <c r="G49">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>183</v>
       </c>
@@ -3270,11 +3225,8 @@
       <c r="E50" t="s">
         <v>37</v>
       </c>
-      <c r="G50">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>28</v>
       </c>
@@ -3290,11 +3242,8 @@
       <c r="E51" t="s">
         <v>130</v>
       </c>
-      <c r="G51">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>211</v>
       </c>
@@ -3310,11 +3259,8 @@
       <c r="E52" t="s">
         <v>32</v>
       </c>
-      <c r="G52">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -3330,11 +3276,8 @@
       <c r="E53" t="s">
         <v>218</v>
       </c>
-      <c r="G53">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -3350,11 +3293,8 @@
       <c r="E54" t="s">
         <v>22</v>
       </c>
-      <c r="G54">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>75</v>
       </c>
@@ -3370,11 +3310,8 @@
       <c r="E55" t="s">
         <v>98</v>
       </c>
-      <c r="G55">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>148</v>
       </c>
@@ -3390,11 +3327,8 @@
       <c r="E56" t="s">
         <v>228</v>
       </c>
-      <c r="G56">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>49</v>
       </c>
@@ -3410,11 +3344,8 @@
       <c r="E57" t="s">
         <v>232</v>
       </c>
-      <c r="G57">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>28</v>
       </c>
@@ -3430,11 +3361,8 @@
       <c r="E58" t="s">
         <v>32</v>
       </c>
-      <c r="G58">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>236</v>
       </c>
@@ -3450,11 +3378,8 @@
       <c r="E59" t="s">
         <v>240</v>
       </c>
-      <c r="G59">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>75</v>
       </c>
@@ -3470,11 +3395,8 @@
       <c r="E60" t="s">
         <v>70</v>
       </c>
-      <c r="G60">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>191</v>
       </c>
@@ -3490,11 +3412,8 @@
       <c r="E61" t="s">
         <v>247</v>
       </c>
-      <c r="G61">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>248</v>
       </c>
@@ -3510,11 +3429,8 @@
       <c r="E62" t="s">
         <v>252</v>
       </c>
-      <c r="G62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>248</v>
       </c>
@@ -3530,11 +3446,8 @@
       <c r="E63" t="s">
         <v>252</v>
       </c>
-      <c r="G63">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>256</v>
       </c>
@@ -3550,11 +3463,8 @@
       <c r="E64" t="s">
         <v>260</v>
       </c>
-      <c r="G64">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>28</v>
       </c>
@@ -3570,11 +3480,8 @@
       <c r="E65" t="s">
         <v>169</v>
       </c>
-      <c r="G65">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>144</v>
       </c>
@@ -3590,11 +3497,8 @@
       <c r="E66" t="s">
         <v>267</v>
       </c>
-      <c r="G66">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>268</v>
       </c>
@@ -3610,11 +3514,8 @@
       <c r="E67" t="s">
         <v>27</v>
       </c>
-      <c r="G67">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>236</v>
       </c>
@@ -3630,11 +3531,8 @@
       <c r="E68" t="s">
         <v>228</v>
       </c>
-      <c r="G68">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>57</v>
       </c>
@@ -3650,11 +3548,8 @@
       <c r="E69" t="s">
         <v>27</v>
       </c>
-      <c r="G69">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -3670,11 +3565,8 @@
       <c r="E70" t="s">
         <v>70</v>
       </c>
-      <c r="G70">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>57</v>
       </c>
@@ -3690,11 +3582,8 @@
       <c r="E71" t="s">
         <v>284</v>
       </c>
-      <c r="G71">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>23</v>
       </c>
@@ -3710,11 +3599,8 @@
       <c r="E72" t="s">
         <v>288</v>
       </c>
-      <c r="G72">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>236</v>
       </c>
@@ -3730,11 +3616,8 @@
       <c r="E73" t="s">
         <v>292</v>
       </c>
-      <c r="G73">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>293</v>
       </c>
@@ -3750,11 +3633,8 @@
       <c r="E74" t="s">
         <v>297</v>
       </c>
-      <c r="G74">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>23</v>
       </c>
@@ -3770,11 +3650,8 @@
       <c r="E75" t="s">
         <v>98</v>
       </c>
-      <c r="G75">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -3790,11 +3667,8 @@
       <c r="E76" t="s">
         <v>70</v>
       </c>
-      <c r="G76">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>144</v>
       </c>
@@ -3810,11 +3684,8 @@
       <c r="E77" t="s">
         <v>307</v>
       </c>
-      <c r="G77">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>38</v>
       </c>
@@ -3830,11 +3701,8 @@
       <c r="E78" t="s">
         <v>113</v>
       </c>
-      <c r="G78">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -3850,11 +3718,8 @@
       <c r="E79" t="s">
         <v>314</v>
       </c>
-      <c r="G79">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>66</v>
       </c>
@@ -3870,11 +3735,8 @@
       <c r="E80" t="s">
         <v>70</v>
       </c>
-      <c r="G80">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>318</v>
       </c>
@@ -3890,11 +3752,8 @@
       <c r="E81" t="s">
         <v>322</v>
       </c>
-      <c r="G81">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>323</v>
       </c>
@@ -3910,11 +3769,8 @@
       <c r="E82" t="s">
         <v>327</v>
       </c>
-      <c r="G82">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>211</v>
       </c>
@@ -3930,11 +3786,8 @@
       <c r="E83" t="s">
         <v>98</v>
       </c>
-      <c r="G83">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>144</v>
       </c>
@@ -3950,11 +3803,8 @@
       <c r="E84" t="s">
         <v>334</v>
       </c>
-      <c r="G84">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>82</v>
       </c>
@@ -3970,11 +3820,8 @@
       <c r="E85" t="s">
         <v>338</v>
       </c>
-      <c r="G85">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>248</v>
       </c>
@@ -3990,11 +3837,8 @@
       <c r="E86" t="s">
         <v>342</v>
       </c>
-      <c r="G86">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>343</v>
       </c>
@@ -4010,11 +3854,8 @@
       <c r="E87" t="s">
         <v>347</v>
       </c>
-      <c r="G87">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>348</v>
       </c>
@@ -4030,11 +3871,8 @@
       <c r="E88" t="s">
         <v>32</v>
       </c>
-      <c r="G88">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>33</v>
       </c>
@@ -4050,11 +3888,8 @@
       <c r="E89" t="s">
         <v>355</v>
       </c>
-      <c r="G89">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>122</v>
       </c>
@@ -4070,11 +3905,8 @@
       <c r="E90" t="s">
         <v>126</v>
       </c>
-      <c r="G90">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>28</v>
       </c>
@@ -4090,11 +3922,8 @@
       <c r="E91" t="s">
         <v>32</v>
       </c>
-      <c r="G91">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>170</v>
       </c>
@@ -4110,11 +3939,8 @@
       <c r="E92" t="s">
         <v>365</v>
       </c>
-      <c r="G92">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>33</v>
       </c>
@@ -4130,11 +3956,8 @@
       <c r="E93" t="s">
         <v>369</v>
       </c>
-      <c r="G93">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>13</v>
       </c>
@@ -4150,11 +3973,8 @@
       <c r="E94" t="s">
         <v>373</v>
       </c>
-      <c r="G94">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>57</v>
       </c>
@@ -4170,11 +3990,8 @@
       <c r="E95" t="s">
         <v>377</v>
       </c>
-      <c r="G95">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>170</v>
       </c>
@@ -4190,11 +4007,8 @@
       <c r="E96" t="s">
         <v>381</v>
       </c>
-      <c r="G96">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>170</v>
       </c>
@@ -4210,11 +4024,8 @@
       <c r="E97" t="s">
         <v>174</v>
       </c>
-      <c r="G97">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>385</v>
       </c>
@@ -4230,11 +4041,8 @@
       <c r="E98" t="s">
         <v>113</v>
       </c>
-      <c r="G98">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>61</v>
       </c>
@@ -4250,11 +4058,8 @@
       <c r="E99" t="s">
         <v>392</v>
       </c>
-      <c r="G99">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>393</v>
       </c>
@@ -4270,11 +4075,8 @@
       <c r="E100" t="s">
         <v>397</v>
       </c>
-      <c r="G100">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>57</v>
       </c>
@@ -4290,11 +4092,8 @@
       <c r="E101" t="s">
         <v>17</v>
       </c>
-      <c r="G101">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>57</v>
       </c>
@@ -4310,11 +4109,8 @@
       <c r="E102" t="s">
         <v>130</v>
       </c>
-      <c r="G102">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>191</v>
       </c>
@@ -4330,11 +4126,8 @@
       <c r="E103" t="s">
         <v>407</v>
       </c>
-      <c r="G103">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>256</v>
       </c>
@@ -4350,11 +4143,8 @@
       <c r="E104" t="s">
         <v>260</v>
       </c>
-      <c r="G104">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>170</v>
       </c>
@@ -4370,11 +4160,8 @@
       <c r="E105" t="s">
         <v>174</v>
       </c>
-      <c r="G105">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>236</v>
       </c>
@@ -4390,11 +4177,8 @@
       <c r="E106" t="s">
         <v>12</v>
       </c>
-      <c r="G106">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>49</v>
       </c>
@@ -4410,11 +4194,8 @@
       <c r="E107" t="s">
         <v>420</v>
       </c>
-      <c r="G107">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>348</v>
       </c>
@@ -4430,11 +4211,8 @@
       <c r="E108" t="s">
         <v>169</v>
       </c>
-      <c r="G108">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>28</v>
       </c>
@@ -4450,11 +4228,8 @@
       <c r="E109" t="s">
         <v>90</v>
       </c>
-      <c r="G109">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>248</v>
       </c>
@@ -4470,11 +4245,8 @@
       <c r="E110" t="s">
         <v>430</v>
       </c>
-      <c r="G110">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>385</v>
       </c>
@@ -4490,11 +4262,8 @@
       <c r="E111" t="s">
         <v>113</v>
       </c>
-      <c r="G111">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>28</v>
       </c>
@@ -4510,11 +4279,8 @@
       <c r="E112" t="s">
         <v>437</v>
       </c>
-      <c r="G112">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>438</v>
       </c>
@@ -4530,11 +4296,8 @@
       <c r="E113" t="s">
         <v>442</v>
       </c>
-      <c r="G113">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>28</v>
       </c>
@@ -4550,11 +4313,8 @@
       <c r="E114" t="s">
         <v>437</v>
       </c>
-      <c r="G114">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>38</v>
       </c>
@@ -4570,11 +4330,8 @@
       <c r="E115" t="s">
         <v>449</v>
       </c>
-      <c r="G115">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>450</v>
       </c>
@@ -4590,11 +4347,8 @@
       <c r="E116" t="s">
         <v>454</v>
       </c>
-      <c r="G116">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>66</v>
       </c>
@@ -4610,11 +4364,8 @@
       <c r="E117" t="s">
         <v>27</v>
       </c>
-      <c r="G117">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>385</v>
       </c>
@@ -4630,11 +4381,8 @@
       <c r="E118" t="s">
         <v>42</v>
       </c>
-      <c r="G118">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>170</v>
       </c>
@@ -4650,11 +4398,8 @@
       <c r="E119" t="s">
         <v>252</v>
       </c>
-      <c r="G119">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>66</v>
       </c>
@@ -4670,11 +4415,8 @@
       <c r="E120" t="s">
         <v>437</v>
       </c>
-      <c r="G120">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>348</v>
       </c>
@@ -4690,11 +4432,8 @@
       <c r="E121" t="s">
         <v>17</v>
       </c>
-      <c r="G121">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>49</v>
       </c>
@@ -4710,11 +4449,8 @@
       <c r="E122" t="s">
         <v>178</v>
       </c>
-      <c r="G122">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>236</v>
       </c>
@@ -4730,11 +4466,8 @@
       <c r="E123" t="s">
         <v>476</v>
       </c>
-      <c r="G123">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>477</v>
       </c>
@@ -4750,11 +4483,8 @@
       <c r="E124" t="s">
         <v>481</v>
       </c>
-      <c r="G124">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>61</v>
       </c>
@@ -4770,11 +4500,8 @@
       <c r="E125" t="s">
         <v>485</v>
       </c>
-      <c r="G125">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>8</v>
       </c>
@@ -4790,11 +4517,8 @@
       <c r="E126" t="s">
         <v>489</v>
       </c>
-      <c r="G126">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -4810,11 +4534,8 @@
       <c r="E127" t="s">
         <v>17</v>
       </c>
-      <c r="G127">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -4830,11 +4551,8 @@
       <c r="E128" t="s">
         <v>496</v>
       </c>
-      <c r="G128">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>8</v>
       </c>
@@ -4850,11 +4568,8 @@
       <c r="E129" t="s">
         <v>12</v>
       </c>
-      <c r="G129">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>75</v>
       </c>
@@ -4870,11 +4585,8 @@
       <c r="E130" t="s">
         <v>288</v>
       </c>
-      <c r="G130">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>211</v>
       </c>
@@ -4890,11 +4602,8 @@
       <c r="E131" t="s">
         <v>496</v>
       </c>
-      <c r="G131">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>23</v>
       </c>
@@ -4910,11 +4619,8 @@
       <c r="E132" t="s">
         <v>70</v>
       </c>
-      <c r="G132">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>148</v>
       </c>
@@ -4930,11 +4636,8 @@
       <c r="E133" t="s">
         <v>512</v>
       </c>
-      <c r="G133">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>513</v>
       </c>
@@ -4950,11 +4653,8 @@
       <c r="E134" t="s">
         <v>517</v>
       </c>
-      <c r="G134">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>236</v>
       </c>
@@ -4970,11 +4670,8 @@
       <c r="E135" t="s">
         <v>12</v>
       </c>
-      <c r="G135">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>170</v>
       </c>
@@ -4990,11 +4687,8 @@
       <c r="E136" t="s">
         <v>174</v>
       </c>
-      <c r="G136">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>122</v>
       </c>
@@ -5010,11 +4704,8 @@
       <c r="E137" t="s">
         <v>528</v>
       </c>
-      <c r="G137">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>236</v>
       </c>
@@ -5030,11 +4721,8 @@
       <c r="E138" t="s">
         <v>476</v>
       </c>
-      <c r="G138">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -5050,11 +4738,8 @@
       <c r="E139" t="s">
         <v>535</v>
       </c>
-      <c r="G139">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>236</v>
       </c>
@@ -5070,11 +4755,8 @@
       <c r="E140" t="s">
         <v>539</v>
       </c>
-      <c r="G140">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>268</v>
       </c>
@@ -5090,11 +4772,8 @@
       <c r="E141" t="s">
         <v>70</v>
       </c>
-      <c r="G141">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -5110,11 +4789,8 @@
       <c r="E142" t="s">
         <v>546</v>
       </c>
-      <c r="G142">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>547</v>
       </c>
@@ -5130,11 +4806,8 @@
       <c r="E143" t="s">
         <v>551</v>
       </c>
-      <c r="G143">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>236</v>
       </c>
@@ -5149,9 +4822,6 @@
       </c>
       <c r="E144" t="s">
         <v>228</v>
-      </c>
-      <c r="G144">
-        <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
@@ -5170,9 +4840,6 @@
       <c r="E145" t="s">
         <v>22</v>
       </c>
-      <c r="G145">
-        <v>144</v>
-      </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
@@ -5190,9 +4857,6 @@
       <c r="E146" t="s">
         <v>561</v>
       </c>
-      <c r="G146">
-        <v>145</v>
-      </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
@@ -5210,9 +4874,6 @@
       <c r="E147" t="s">
         <v>288</v>
       </c>
-      <c r="G147">
-        <v>146</v>
-      </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
@@ -5230,9 +4891,6 @@
       <c r="E148" t="s">
         <v>32</v>
       </c>
-      <c r="G148">
-        <v>147</v>
-      </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
@@ -5250,9 +4908,6 @@
       <c r="E149" t="s">
         <v>476</v>
       </c>
-      <c r="G149">
-        <v>148</v>
-      </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
@@ -5270,9 +4925,6 @@
       <c r="E150" t="s">
         <v>574</v>
       </c>
-      <c r="G150">
-        <v>149</v>
-      </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
@@ -5290,9 +4942,6 @@
       <c r="E151" t="s">
         <v>27</v>
       </c>
-      <c r="G151">
-        <v>150</v>
-      </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
@@ -5310,9 +4959,6 @@
       <c r="E152" t="s">
         <v>524</v>
       </c>
-      <c r="G152">
-        <v>151</v>
-      </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
@@ -5330,9 +4976,6 @@
       <c r="E153" t="s">
         <v>585</v>
       </c>
-      <c r="G153">
-        <v>152</v>
-      </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
@@ -5350,9 +4993,6 @@
       <c r="E154" t="s">
         <v>260</v>
       </c>
-      <c r="G154">
-        <v>153</v>
-      </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
@@ -5370,9 +5010,6 @@
       <c r="E155" t="s">
         <v>70</v>
       </c>
-      <c r="G155">
-        <v>154</v>
-      </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
@@ -5390,9 +5027,6 @@
       <c r="E156" t="s">
         <v>595</v>
       </c>
-      <c r="G156">
-        <v>155</v>
-      </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
@@ -5410,9 +5044,6 @@
       <c r="E157" t="s">
         <v>17</v>
       </c>
-      <c r="G157">
-        <v>156</v>
-      </c>
       <c r="I157" t="s">
         <v>612</v>
       </c>
@@ -5433,9 +5064,6 @@
       <c r="E158" t="s">
         <v>27</v>
       </c>
-      <c r="G158">
-        <v>157</v>
-      </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
@@ -5453,9 +5081,6 @@
       <c r="E159" t="s">
         <v>98</v>
       </c>
-      <c r="G159">
-        <v>158</v>
-      </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
@@ -5473,11 +5098,8 @@
       <c r="E160" t="s">
         <v>476</v>
       </c>
-      <c r="G160">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>49</v>
       </c>
@@ -5493,12 +5115,147 @@
       <c r="E161" t="s">
         <v>611</v>
       </c>
-      <c r="G161">
-        <v>160</v>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>613</v>
+      </c>
+      <c r="B162" t="s">
+        <v>614</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D162" t="s">
+        <v>616</v>
+      </c>
+      <c r="E162" t="s">
+        <v>27</v>
+      </c>
+      <c r="F162" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>613</v>
+      </c>
+      <c r="B163" t="s">
+        <v>618</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="D163" t="s">
+        <v>620</v>
+      </c>
+      <c r="E163" t="s">
+        <v>27</v>
+      </c>
+      <c r="F163" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>613</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D164" t="s">
+        <v>623</v>
+      </c>
+      <c r="E164" t="s">
+        <v>624</v>
+      </c>
+      <c r="F164" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>613</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="D165" t="s">
+        <v>627</v>
+      </c>
+      <c r="E165" t="s">
+        <v>624</v>
+      </c>
+      <c r="F165" t="s">
+        <v>617</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G161" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I165" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="B164" r:id="rId1" xr:uid="{C527B6FD-E880-4FD5-943B-4B18404F806A}"/>
+    <hyperlink ref="B165" r:id="rId2" xr:uid="{9217E106-EFFB-4DE6-8085-4DE1446442BC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498AF496-BA5F-4FC0-AAF7-92885505A00F}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>619</v>
+      </c>
+      <c r="B3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>622</v>
+      </c>
+      <c r="B4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>626</v>
+      </c>
+      <c r="B5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
